--- a/self_dataset/compare_results/TOD.xlsx
+++ b/self_dataset/compare_results/TOD.xlsx
@@ -420,13 +420,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>buggy_2_CareerOnToken.txt</t>
+          <t>buggy_11_ForTheBlockchain.txt</t>
         </is>
       </c>
     </row>
@@ -468,16 +468,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -485,19 +485,19 @@
         <v>114</v>
       </c>
       <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
         <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>buggy_3_CareerOnToken.txt</t>
+          <t>buggy_11_Owned.txt</t>
         </is>
       </c>
     </row>
@@ -525,159 +525,159 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>114</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>buggy_14_ERC20.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>buggy_14_SaveWon.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114</v>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>buggy_17_AZT.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>101</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>110</v>
       </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>114</v>
-      </c>
-      <c r="B10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>buggy_4_PHO.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>101</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>114</v>
-      </c>
-      <c r="B15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>buggy_6_ChannelWallet.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>114</v>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>buggy_7_AccountWallet.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -685,22 +685,736 @@
         <v>114</v>
       </c>
       <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="n">
         <v>2</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
       <c r="D23" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>buggy_17_owned.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>114</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>buggy_18_Owned.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>114</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>buggy_19_ethBank.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>114</v>
+      </c>
+      <c r="B35" t="n">
+        <v>6</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>buggy_19_owned.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>114</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>buggy_1_HotDollarsToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>101</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>114</v>
+      </c>
+      <c r="B44" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>buggy_20_Stoppable.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>114</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>buggy_2_CareerOnToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>101</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>110</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>114</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>buggy_3_CareerOnToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>110</v>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>114</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4</v>
+      </c>
+      <c r="C59" t="n">
+        <v>7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>buggy_4_PHO.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>101</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>114</v>
+      </c>
+      <c r="B64" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" t="n">
+        <v>9</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>buggy_5_Ownable.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>114</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>buggy_6_ChannelWallet.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>114</v>
+      </c>
+      <c r="B72" t="n">
+        <v>12</v>
+      </c>
+      <c r="C72" t="n">
+        <v>13</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>buggy_7_AccountWallet.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>114</v>
+      </c>
+      <c r="B76" t="n">
+        <v>7</v>
+      </c>
+      <c r="C76" t="n">
+        <v>8</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>buggy_8_Ownable.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>114</v>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>buggy_9_XLToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>101</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" t="n">
+        <v>6</v>
+      </c>
+      <c r="D84" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>110</v>
+      </c>
+      <c r="B85" t="n">
+        <v>2</v>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>114</v>
+      </c>
+      <c r="B86" t="n">
+        <v>10</v>
+      </c>
+      <c r="C86" t="n">
+        <v>8</v>
+      </c>
+      <c r="D86" t="n">
         <v>-2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="19">
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A78:D78"/>
     <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
